--- a/Data/SummonPrice.xlsx
+++ b/Data/SummonPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999A3D55-85D6-4BB8-91FC-65B0EACE6474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DE44F3-9B08-46E2-928F-3A607270DE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6660" yWindow="1935" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SummonPrice" sheetId="1" r:id="rId1"/>
@@ -552,7 +552,7 @@
         <v>1001</v>
       </c>
       <c r="E2" s="6">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F2" s="6">
         <v>2</v>
@@ -572,7 +572,7 @@
         <v>1001</v>
       </c>
       <c r="E3" s="6">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F3" s="6">
         <v>2</v>
